--- a/projects/xiuxian/game/data/table/资源配置.xlsx
+++ b/projects/xiuxian/game/data/table/资源配置.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,18 +551,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mortal_pill</t>
+          <t>beast_blood</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>凡品丹药</t>
+          <t>兽血</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>material</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -570,7 +570,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>回复体力 / 消除轻伤 / 短期 buff</t>
+          <t>炼丹原料，历练战利品</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -578,18 +578,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>yellow_pill</t>
+          <t>demon_core</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>黄品丹药</t>
+          <t>妖丹</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>material</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>中阶丹药</t>
+          <t>妖兽内丹，高阶炼丹原料</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -605,26 +605,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mystic_pill</t>
+          <t>fire_essence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>玄品丹药</t>
+          <t>火精</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>material</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>高阶丹药</t>
+          <t>火属性精华，灵根丹原料</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -632,18 +632,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>breakthrough_pill_qi</t>
+          <t>millennium_herb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>炼气突破丹</t>
+          <t>千年灵芝</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>material</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>炼气境突破检定时消耗，提升基础概率</t>
+          <t>稀有药材，寿元丹原料</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -659,29 +659,153 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>mortal_pill</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>凡品丹药</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>res://art/m3/icons/pill_mortal.png</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>回复体力 / 消除轻伤 / 短期 buff</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>yellow_pill</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>黄品丹药</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>res://art/m3/icons/pill_yellow.png</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>中阶丹药</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mystic_pill</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>玄品丹药</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>res://art/m3/icons/pill_mystic.png</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>99</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>高阶丹药</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>breakthrough_pill_qi</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>炼气突破丹</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>res://art/m3/icons/pill_breakthrough.png</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>99</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>炼气境突破检定时消耗，提升基础概率</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>sect_token</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>宗门令牌</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>treasure</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>宗门权柄象征</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
